--- a/analysis/statistics/Effect_Sizes_Table.xlsx
+++ b/analysis/statistics/Effect_Sizes_Table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="820" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1094" uniqueCount="32">
   <si>
     <t>Flavor</t>
   </si>
@@ -157,17 +157,17 @@
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="true"/>
-    <col min="2" max="2" width="11.42578125" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="12.42578125" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" customWidth="true"/>
-    <col min="7" max="7" width="20.140625" customWidth="true"/>
-    <col min="8" max="8" width="12.7109375" customWidth="true"/>
-    <col min="9" max="9" width="15.7109375" customWidth="true"/>
-    <col min="10" max="10" width="13.7109375" customWidth="true"/>
-    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="1" max="1" width="26.6640625" customWidth="true"/>
+    <col min="2" max="2" width="10.33203125" customWidth="true"/>
+    <col min="3" max="3" width="14" customWidth="true"/>
+    <col min="4" max="4" width="11.33203125" customWidth="true"/>
+    <col min="5" max="5" width="15.21875" customWidth="true"/>
+    <col min="6" max="6" width="14.5546875" customWidth="true"/>
+    <col min="7" max="7" width="18.5546875" customWidth="true"/>
+    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="9" max="9" width="14" customWidth="true"/>
+    <col min="10" max="10" width="13.5546875" customWidth="true"/>
+    <col min="11" max="11" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -234,10 +234,10 @@
         <v>0.39445862649764069</v>
       </c>
       <c r="J2" s="0">
-        <v>0.033921100250688091</v>
+        <v>0.034437963114495235</v>
       </c>
       <c r="K2" s="0">
-        <v>1.0522162297007249</v>
+        <v>1.0641714868069585</v>
       </c>
     </row>
     <row r="3">
@@ -269,10 +269,10 @@
         <v>1.198624010418879</v>
       </c>
       <c r="J3" s="0">
-        <v>0.82616492936641883</v>
+        <v>0.83018561470691987</v>
       </c>
       <c r="K3" s="0">
-        <v>1.7391178793745965</v>
+        <v>1.7162585251320768</v>
       </c>
     </row>
     <row r="4">
@@ -304,10 +304,10 @@
         <v>0.84301000627073119</v>
       </c>
       <c r="J4" s="0">
-        <v>0.37764475707626233</v>
+        <v>0.38315346365646574</v>
       </c>
       <c r="K4" s="0">
-        <v>1.5285512913696082</v>
+        <v>1.5181618408841964</v>
       </c>
     </row>
     <row r="5">
@@ -339,10 +339,10 @@
         <v>0.28612353450934941</v>
       </c>
       <c r="J5" s="0">
-        <v>0.059935135674682283</v>
+        <v>0.065517180129528785</v>
       </c>
       <c r="K5" s="0">
-        <v>0.76563288670740493</v>
+        <v>0.75720008336742262</v>
       </c>
     </row>
     <row r="6">
@@ -374,10 +374,10 @@
         <v>0.9746800462874059</v>
       </c>
       <c r="J6" s="0">
-        <v>0.5060265060356608</v>
+        <v>0.50023805652220088</v>
       </c>
       <c r="K6" s="0">
-        <v>1.4909450461848008</v>
+        <v>1.4930464436615853</v>
       </c>
     </row>
     <row r="7">
@@ -409,10 +409,10 @@
         <v>0.66180748454850136</v>
       </c>
       <c r="J7" s="0">
-        <v>0.28773348450085617</v>
+        <v>0.28178496488343319</v>
       </c>
       <c r="K7" s="0">
-        <v>1.1988172363040359</v>
+        <v>1.2077505186970385</v>
       </c>
     </row>
     <row r="8">
@@ -444,10 +444,10 @@
         <v>0.15588479766047661</v>
       </c>
       <c r="J8" s="0">
-        <v>0.013275478064749192</v>
+        <v>0.013028274568312083</v>
       </c>
       <c r="K8" s="0">
-        <v>0.57938241692019399</v>
+        <v>0.58478656183762245</v>
       </c>
     </row>
     <row r="9">
@@ -479,10 +479,10 @@
         <v>0.62903306266704784</v>
       </c>
       <c r="J9" s="0">
-        <v>0.36693764335678669</v>
+        <v>0.36282991684869137</v>
       </c>
       <c r="K9" s="0">
-        <v>1.158222880717124</v>
+        <v>1.1628132666772479</v>
       </c>
     </row>
     <row r="10">
@@ -514,10 +514,10 @@
         <v>1.1105279392913965</v>
       </c>
       <c r="J10" s="0">
-        <v>0.8437075290074616</v>
+        <v>0.83037937448929089</v>
       </c>
       <c r="K10" s="0">
-        <v>1.7325637136479757</v>
+        <v>1.7123578342080163</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>0.64672994369148595</v>
       </c>
       <c r="J11" s="0">
-        <v>0.39119651096177244</v>
+        <v>0.38331409662339416</v>
       </c>
       <c r="K11" s="0">
-        <v>0.9876436213308023</v>
+        <v>0.9778737377947917</v>
       </c>
     </row>
     <row r="12">
@@ -584,10 +584,10 @@
         <v>0.71402566621136665</v>
       </c>
       <c r="J12" s="0">
-        <v>0.44213211895243149</v>
+        <v>0.43660167813667294</v>
       </c>
       <c r="K12" s="0">
-        <v>1.0694696906824737</v>
+        <v>1.0690391515464599</v>
       </c>
     </row>
     <row r="13">
@@ -619,10 +619,10 @@
         <v>0.71521349767835019</v>
       </c>
       <c r="J13" s="0">
-        <v>0.38750471694812838</v>
+        <v>0.38411703566356209</v>
       </c>
       <c r="K13" s="0">
-        <v>1.138697120328596</v>
+        <v>1.1440059355099073</v>
       </c>
     </row>
     <row r="14">
@@ -654,10 +654,10 @@
         <v>0.23415906670078662</v>
       </c>
       <c r="J14" s="0">
-        <v>0.017326471696972018</v>
+        <v>0.01742244533940749</v>
       </c>
       <c r="K14" s="0">
-        <v>0.49675038893143519</v>
+        <v>0.49710912268412044</v>
       </c>
     </row>
     <row r="15">
@@ -689,10 +689,10 @@
         <v>0.74222660264153839</v>
       </c>
       <c r="J15" s="0">
-        <v>0.4875552465315024</v>
+        <v>0.47617356289494772</v>
       </c>
       <c r="K15" s="0">
-        <v>1.0886132490788349</v>
+        <v>1.0867602275745223</v>
       </c>
     </row>
     <row r="16">
@@ -724,10 +724,10 @@
         <v>0.29481606354331591</v>
       </c>
       <c r="J16" s="0">
-        <v>0.018445314390621994</v>
+        <v>0.01770014130369213</v>
       </c>
       <c r="K16" s="0">
-        <v>0.91532788938616172</v>
+        <v>0.92475080385309794</v>
       </c>
     </row>
     <row r="17">
@@ -759,10 +759,10 @@
         <v>0.89762229115236592</v>
       </c>
       <c r="J17" s="0">
-        <v>0.91927770446369328</v>
+        <v>0.92181753140195222</v>
       </c>
       <c r="K17" s="0">
-        <v>1.553709483235171</v>
+        <v>1.5460451220129734</v>
       </c>
     </row>
     <row r="18">
@@ -794,10 +794,10 @@
         <v>0.92679450166809618</v>
       </c>
       <c r="J18" s="0">
-        <v>0.51345929260817669</v>
+        <v>0.51976820637078669</v>
       </c>
       <c r="K18" s="0">
-        <v>1.6647193672643388</v>
+        <v>1.6444901633603988</v>
       </c>
     </row>
     <row r="19">
@@ -829,10 +829,10 @@
         <v>0.3339530162402084</v>
       </c>
       <c r="J19" s="0">
-        <v>0.14583536356966825</v>
+        <v>0.13290423988398098</v>
       </c>
       <c r="K19" s="0">
-        <v>0.81634266833585678</v>
+        <v>0.81450217791381618</v>
       </c>
     </row>
     <row r="20">
@@ -864,10 +864,10 @@
         <v>1.0461536355695027</v>
       </c>
       <c r="J20" s="0">
-        <v>0.54716498484448317</v>
+        <v>0.53898332459725717</v>
       </c>
       <c r="K20" s="0">
-        <v>1.6009500997851967</v>
+        <v>1.5986702693154902</v>
       </c>
     </row>
     <row r="21">
@@ -899,10 +899,10 @@
         <v>0.73825523350910094</v>
       </c>
       <c r="J21" s="0">
-        <v>0.35468037278450071</v>
+        <v>0.35246568613100948</v>
       </c>
       <c r="K21" s="0">
-        <v>1.2031015408420844</v>
+        <v>1.2148052450551696</v>
       </c>
     </row>
     <row r="22">
@@ -959,10 +959,10 @@
         <v>0.60729183903173689</v>
       </c>
       <c r="J23" s="0">
-        <v>0.33377754944117133</v>
+        <v>0.32360928689404544</v>
       </c>
       <c r="K23" s="0">
-        <v>1.1465854852505957</v>
+        <v>1.1588897211366129</v>
       </c>
     </row>
     <row r="24">
@@ -994,10 +994,10 @@
         <v>1.1105279392913958</v>
       </c>
       <c r="J24" s="0">
-        <v>0.84370752900746115</v>
+        <v>0.83037937448929022</v>
       </c>
       <c r="K24" s="0">
-        <v>1.7325637136479757</v>
+        <v>1.7123578342080155</v>
       </c>
     </row>
     <row r="25">
@@ -1014,25 +1014,25 @@
         <v>0</v>
       </c>
       <c r="E25" s="0">
-        <v>0.58043735126396956</v>
+        <v>1.141015520212296</v>
       </c>
       <c r="F25" s="0">
-        <v>1.4301776701616282</v>
+        <v>1.6214309656212589</v>
       </c>
       <c r="G25" s="0">
-        <v>0.40466142920377962</v>
+        <v>0.70621386493140303</v>
       </c>
       <c r="H25" s="0">
-        <v>0.40466142920377962</v>
+        <v>0.70621386493140303</v>
       </c>
       <c r="I25" s="0">
-        <v>0.40466142920377962</v>
+        <v>0.70621386493140303</v>
       </c>
       <c r="J25" s="0">
-        <v>0.085927143703443981</v>
+        <v>0.38459730394499814</v>
       </c>
       <c r="K25" s="0">
-        <v>0.74875559756071197</v>
+        <v>1.1202848311786899</v>
       </c>
     </row>
     <row r="26">
@@ -1049,25 +1049,25 @@
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>0.010352782299763445</v>
+        <v>0.015874506076300043</v>
       </c>
       <c r="F26" s="0">
-        <v>0.023677496995156758</v>
+        <v>0.022683889790937349</v>
       </c>
       <c r="G26" s="0">
-        <v>0.43398797882460444</v>
+        <v>0.69649344932248602</v>
       </c>
       <c r="H26" s="0">
-        <v>0.43398797882460444</v>
+        <v>0.69649344932248602</v>
       </c>
       <c r="I26" s="0">
-        <v>0.43398797882460444</v>
+        <v>0.69649344932248602</v>
       </c>
       <c r="J26" s="0">
-        <v>0.11426432069308373</v>
+        <v>0.3863654497143425</v>
       </c>
       <c r="K26" s="0">
-        <v>0.77889743086102736</v>
+        <v>1.102930831415184</v>
       </c>
     </row>
     <row r="27">
@@ -1084,25 +1084,25 @@
         <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>0.00087170930637313565</v>
+        <v>0.0069657275596865451</v>
       </c>
       <c r="F27" s="0">
-        <v>0.0027548669254164257</v>
+        <v>0.0099733833139487391</v>
       </c>
       <c r="G27" s="0">
-        <v>0.3087657513153661</v>
+        <v>0.65688749440210714</v>
       </c>
       <c r="H27" s="0">
-        <v>0.3087657513153661</v>
+        <v>0.65688749440210714</v>
       </c>
       <c r="I27" s="0">
-        <v>0.3087657513153661</v>
+        <v>0.65688749440210714</v>
       </c>
       <c r="J27" s="0">
-        <v>0.0282171609857019</v>
+        <v>0.32657842135200155</v>
       </c>
       <c r="K27" s="0">
-        <v>0.63981240109434234</v>
+        <v>1.0749304879119597</v>
       </c>
     </row>
     <row r="28">
@@ -1119,25 +1119,25 @@
         <v>0</v>
       </c>
       <c r="E28" s="0">
-        <v>0.0020884688041377815</v>
+        <v>0.0035467196068677152</v>
       </c>
       <c r="F28" s="0">
-        <v>0.004358394415544079</v>
+        <v>0.0064229099559276071</v>
       </c>
       <c r="G28" s="0">
-        <v>0.35977198349685685</v>
+        <v>0.536505927501708</v>
       </c>
       <c r="H28" s="0">
-        <v>0.35977198349685685</v>
+        <v>0.536505927501708</v>
       </c>
       <c r="I28" s="0">
-        <v>0.35977198349685685</v>
+        <v>0.536505927501708</v>
       </c>
       <c r="J28" s="0">
-        <v>0.11043745459724383</v>
+        <v>0.26521584998629494</v>
       </c>
       <c r="K28" s="0">
-        <v>0.62407144541913528</v>
+        <v>0.83206226015580032</v>
       </c>
     </row>
     <row r="29">
@@ -1194,10 +1194,10 @@
         <v>0.30188009285732004</v>
       </c>
       <c r="J30" s="0">
-        <v>0.020354670696807471</v>
+        <v>0.019504997940095074</v>
       </c>
       <c r="K30" s="0">
-        <v>0.91653713092234135</v>
+        <v>0.93292011050596302</v>
       </c>
     </row>
     <row r="31">
@@ -1229,10 +1229,10 @@
         <v>1.0616161613237478</v>
       </c>
       <c r="J31" s="0">
-        <v>0.98859939216053194</v>
+        <v>0.99240916413541713</v>
       </c>
       <c r="K31" s="0">
-        <v>1.6546770786137322</v>
+        <v>1.6548906322006451</v>
       </c>
     </row>
     <row r="32">
@@ -1264,10 +1264,10 @@
         <v>1.0100496329975559</v>
       </c>
       <c r="J32" s="0">
-        <v>0.51818442614227145</v>
+        <v>0.51478639640112966</v>
       </c>
       <c r="K32" s="0">
-        <v>1.8615228597050717</v>
+        <v>1.8642960852544226</v>
       </c>
     </row>
     <row r="33">
@@ -1299,10 +1299,10 @@
         <v>0.33395301624020834</v>
       </c>
       <c r="J33" s="0">
-        <v>0.14583536356966814</v>
+        <v>0.13290423988398112</v>
       </c>
       <c r="K33" s="0">
-        <v>0.81634266833585678</v>
+        <v>0.81450217791381618</v>
       </c>
     </row>
     <row r="34">
@@ -1334,10 +1334,10 @@
         <v>0.97972428217384622</v>
       </c>
       <c r="J34" s="0">
-        <v>0.48583478081123532</v>
+        <v>0.47562352686946019</v>
       </c>
       <c r="K34" s="0">
-        <v>1.5243006501056577</v>
+        <v>1.511553323166777</v>
       </c>
     </row>
     <row r="35">
@@ -1369,10 +1369,10 @@
         <v>0.73541711430784484</v>
       </c>
       <c r="J35" s="0">
-        <v>0.35722379974731933</v>
+        <v>0.35148208517934665</v>
       </c>
       <c r="K35" s="0">
-        <v>1.2187546696139888</v>
+        <v>1.2290093858575488</v>
       </c>
     </row>
     <row r="36">
@@ -1425,10 +1425,10 @@
         <v>0.60729183903173689</v>
       </c>
       <c r="J37" s="0">
-        <v>0.33377754944117133</v>
+        <v>0.32360928689404544</v>
       </c>
       <c r="K37" s="0">
-        <v>1.1465854852505957</v>
+        <v>1.1588897211366129</v>
       </c>
     </row>
     <row r="38">
@@ -1460,10 +1460,10 @@
         <v>1.0992931512166166</v>
       </c>
       <c r="J38" s="0">
-        <v>0.85159790878316299</v>
+        <v>0.83931159772792485</v>
       </c>
       <c r="K38" s="0">
-        <v>1.7325086473171374</v>
+        <v>1.7134367780561783</v>
       </c>
     </row>
     <row r="39">
@@ -1480,25 +1480,25 @@
         <v>0</v>
       </c>
       <c r="E39" s="0">
-        <v>0.58043735126396956</v>
+        <v>1.141015520212296</v>
       </c>
       <c r="F39" s="0">
-        <v>1.4301776701616282</v>
+        <v>1.6214309656212589</v>
       </c>
       <c r="G39" s="0">
-        <v>0.40466142920377962</v>
+        <v>0.70621386493140303</v>
       </c>
       <c r="H39" s="0">
-        <v>0.40466142920377962</v>
+        <v>0.70621386493140303</v>
       </c>
       <c r="I39" s="0">
-        <v>0.40466142920377962</v>
+        <v>0.70621386493140303</v>
       </c>
       <c r="J39" s="0">
-        <v>0.085927143703443981</v>
+        <v>0.38459730394499814</v>
       </c>
       <c r="K39" s="0">
-        <v>0.74875559756071197</v>
+        <v>1.1202848311786899</v>
       </c>
     </row>
     <row r="40">
@@ -1515,25 +1515,25 @@
         <v>0</v>
       </c>
       <c r="E40" s="0">
-        <v>0.010352782299763445</v>
+        <v>0.015874506076300043</v>
       </c>
       <c r="F40" s="0">
-        <v>0.023677496995156758</v>
+        <v>0.022683889790937349</v>
       </c>
       <c r="G40" s="0">
-        <v>0.43398797882460444</v>
+        <v>0.69649344932248602</v>
       </c>
       <c r="H40" s="0">
-        <v>0.43398797882460444</v>
+        <v>0.69649344932248602</v>
       </c>
       <c r="I40" s="0">
-        <v>0.43398797882460444</v>
+        <v>0.69649344932248602</v>
       </c>
       <c r="J40" s="0">
-        <v>0.11426432069308373</v>
+        <v>0.3863654497143425</v>
       </c>
       <c r="K40" s="0">
-        <v>0.77889743086102736</v>
+        <v>1.102930831415184</v>
       </c>
     </row>
     <row r="41">
@@ -1550,25 +1550,25 @@
         <v>0</v>
       </c>
       <c r="E41" s="0">
-        <v>0.00087170930637313565</v>
+        <v>0.0069657275596865451</v>
       </c>
       <c r="F41" s="0">
-        <v>0.0027548669254164257</v>
+        <v>0.0099733833139487391</v>
       </c>
       <c r="G41" s="0">
-        <v>0.3087657513153661</v>
+        <v>0.65688749440210714</v>
       </c>
       <c r="H41" s="0">
-        <v>0.3087657513153661</v>
+        <v>0.65688749440210714</v>
       </c>
       <c r="I41" s="0">
-        <v>0.3087657513153661</v>
+        <v>0.65688749440210714</v>
       </c>
       <c r="J41" s="0">
-        <v>0.0282171609857019</v>
+        <v>0.32657842135200155</v>
       </c>
       <c r="K41" s="0">
-        <v>0.63981240109434234</v>
+        <v>1.0749304879119597</v>
       </c>
     </row>
     <row r="42">
@@ -1585,25 +1585,25 @@
         <v>0</v>
       </c>
       <c r="E42" s="0">
-        <v>0.0020884688041377815</v>
+        <v>0.0035467196068677152</v>
       </c>
       <c r="F42" s="0">
-        <v>0.004358394415544079</v>
+        <v>0.0064229099559276071</v>
       </c>
       <c r="G42" s="0">
-        <v>0.35977198349685685</v>
+        <v>0.536505927501708</v>
       </c>
       <c r="H42" s="0">
-        <v>0.35977198349685685</v>
+        <v>0.536505927501708</v>
       </c>
       <c r="I42" s="0">
-        <v>0.35977198349685685</v>
+        <v>0.536505927501708</v>
       </c>
       <c r="J42" s="0">
-        <v>0.11043745459724383</v>
+        <v>0.26521584998629494</v>
       </c>
       <c r="K42" s="0">
-        <v>0.62407144541913528</v>
+        <v>0.83206226015580032</v>
       </c>
     </row>
     <row r="43">
